--- a/exports/trend_1d/RVNL_full_report.xlsx
+++ b/exports/trend_1d/RVNL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.87</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H2" t="n">
-        <v>26.05</v>
+        <v>25.6</v>
       </c>
       <c r="I2" t="n">
         <v>25.64529045435788</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K2" t="n">
-        <v>18.14</v>
+        <v>16.1</v>
       </c>
       <c r="L2" t="n">
         <v>3.85</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>11.71</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H3" t="n">
-        <v>24.35</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
         <v>25.56182375884103</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.88</v>
+        <v>-1.56</v>
       </c>
       <c r="L3" t="n">
-        <v>2.34</v>
+        <v>3.12</v>
       </c>
       <c r="M3" t="n">
         <v>1.27</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>6.78</v>
       </c>
       <c r="O3" t="n">
         <v>-1.73</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43818</v>
+        <v>43819</v>
       </c>
       <c r="H4" t="n">
-        <v>23.15</v>
+        <v>22.85</v>
       </c>
       <c r="I4" t="n">
         <v>22.89005555907134</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.96</v>
+        <v>-12.12</v>
       </c>
       <c r="L4" t="n">
         <v>13.46</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>6.42</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43832</v>
+        <v>43833</v>
       </c>
       <c r="H5" t="n">
-        <v>23.75</v>
+        <v>25.05</v>
       </c>
       <c r="I5" t="n">
         <v>24.14044990541419</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.94</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>10.72</v>
       </c>
       <c r="M5" t="n">
         <v>0.88</v>
       </c>
       <c r="N5" t="n">
-        <v>3.26</v>
+        <v>5.47</v>
       </c>
       <c r="O5" t="n">
         <v>-1.3</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H6" t="n">
-        <v>27.35</v>
+        <v>24.9</v>
       </c>
       <c r="I6" t="n">
         <v>25.04716310047776</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>9.18</v>
+        <v>-0.6</v>
       </c>
       <c r="L6" t="n">
         <v>5.79</v>
@@ -783,7 +854,7 @@
         <v>2.24</v>
       </c>
       <c r="N6" t="n">
-        <v>4.79</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>5.47</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>22.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H7" t="n">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="I7" t="n">
         <v>15.84731100068886</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K7" t="n">
-        <v>38.96</v>
+        <v>32.93</v>
       </c>
       <c r="L7" t="n">
         <v>13.25</v>
       </c>
       <c r="M7" t="n">
-        <v>5.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>9.869999999999999</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>28.47</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H8" t="n">
-        <v>21.35</v>
+        <v>20.35</v>
       </c>
       <c r="I8" t="n">
         <v>20.53586187440726</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K8" t="n">
-        <v>27.84</v>
+        <v>21.86</v>
       </c>
       <c r="L8" t="n">
         <v>5.69</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.32</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44155</v>
+        <v>44158</v>
       </c>
       <c r="H9" t="n">
-        <v>19.25</v>
+        <v>20.7</v>
       </c>
       <c r="I9" t="n">
         <v>19.30521495153501</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>5.41</v>
+        <v>-1.72</v>
       </c>
       <c r="L9" t="n">
         <v>5.9</v>
@@ -954,7 +1061,7 @@
         <v>2.34</v>
       </c>
       <c r="N9" t="n">
-        <v>2.99</v>
+        <v>7.53</v>
       </c>
       <c r="O9" t="n">
         <v>-4.68</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.87</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44174</v>
+        <v>44175</v>
       </c>
       <c r="H10" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="I10" t="n">
         <v>22.39436049397445</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>10.14</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>6.04</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>13.37</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44200</v>
+        <v>44201</v>
       </c>
       <c r="H11" t="n">
-        <v>24.05</v>
+        <v>27.4</v>
       </c>
       <c r="I11" t="n">
         <v>24.82908619989263</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.82</v>
+        <v>-25.11</v>
       </c>
       <c r="L11" t="n">
-        <v>11.87</v>
+        <v>29.68</v>
       </c>
       <c r="M11" t="n">
         <v>2.19</v>
       </c>
       <c r="N11" t="n">
-        <v>6.85</v>
+        <v>13.93</v>
       </c>
       <c r="O11" t="n">
         <v>-3.95</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>18.59</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H12" t="n">
-        <v>30.05</v>
+        <v>28.95</v>
       </c>
       <c r="I12" t="n">
         <v>29.14822969459134</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>9.67</v>
+        <v>5.66</v>
       </c>
       <c r="L12" t="n">
         <v>12.23</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>18.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H13" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="I13" t="n">
         <v>29.70795251449896</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.25</v>
+        <v>-2.94</v>
       </c>
       <c r="L13" t="n">
         <v>15.54</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H14" t="n">
-        <v>31.1</v>
+        <v>30.4</v>
       </c>
       <c r="I14" t="n">
         <v>30.47505061541352</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K14" t="n">
-        <v>4.36</v>
+        <v>2.01</v>
       </c>
       <c r="L14" t="n">
         <v>3.86</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44441</v>
+        <v>44442</v>
       </c>
       <c r="H15" t="n">
-        <v>28.15</v>
+        <v>30</v>
       </c>
       <c r="I15" t="n">
         <v>29.85915238576985</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K15" t="n">
-        <v>7.4</v>
+        <v>1.32</v>
       </c>
       <c r="L15" t="n">
         <v>2.8</v>
@@ -1296,7 +1475,7 @@
         <v>3.04</v>
       </c>
       <c r="N15" t="n">
-        <v>1.89</v>
+        <v>6.57</v>
       </c>
       <c r="O15" t="n">
         <v>-2.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H16" t="n">
-        <v>35.05</v>
+        <v>33.25</v>
       </c>
       <c r="I16" t="n">
         <v>33.93649887037026</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K16" t="n">
-        <v>16.83</v>
+        <v>10.83</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>18.2</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H17" t="n">
-        <v>36.35</v>
+        <v>38.4</v>
       </c>
       <c r="I17" t="n">
         <v>36.73844115232667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.32</v>
+        <v>-15.49</v>
       </c>
       <c r="L17" t="n">
-        <v>12.48</v>
+        <v>18.2</v>
       </c>
       <c r="M17" t="n">
         <v>4.48</v>
       </c>
       <c r="N17" t="n">
-        <v>4.31</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
         <v>-5.14</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.36</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44599</v>
+        <v>44600</v>
       </c>
       <c r="H18" t="n">
-        <v>34.85</v>
+        <v>34.45</v>
       </c>
       <c r="I18" t="n">
         <v>34.52929645741179</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.24</v>
+        <v>-10.29</v>
       </c>
       <c r="L18" t="n">
-        <v>10.16</v>
+        <v>11.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.27</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>10.72</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H19" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
       <c r="I19" t="n">
         <v>33.66169578735381</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K19" t="n">
-        <v>3.77</v>
+        <v>-0.29</v>
       </c>
       <c r="L19" t="n">
         <v>4.21</v>
       </c>
       <c r="M19" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="N19" t="n">
         <v>6.16</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44649</v>
+        <v>44650</v>
       </c>
       <c r="H20" t="n">
-        <v>33.25</v>
+        <v>32.6</v>
       </c>
       <c r="I20" t="n">
         <v>32.83434057155826</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.76</v>
+        <v>-5.64</v>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>5.93</v>
       </c>
       <c r="M20" t="n">
         <v>3.04</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44798</v>
+        <v>44799</v>
       </c>
       <c r="H21" t="n">
-        <v>31.55</v>
+        <v>32.3</v>
       </c>
       <c r="I21" t="n">
         <v>31.98317261279891</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K21" t="n">
-        <v>3.22</v>
+        <v>0.92</v>
       </c>
       <c r="L21" t="n">
         <v>14.72</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H22" t="n">
-        <v>66.45</v>
+        <v>63.15</v>
       </c>
       <c r="I22" t="n">
         <v>64.86099275478821</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K22" t="n">
-        <v>105.73</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>2.48</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>21.23</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44937</v>
+        <v>44938</v>
       </c>
       <c r="H23" t="n">
-        <v>72.2</v>
+        <v>75.8</v>
       </c>
       <c r="I23" t="n">
         <v>75.17976041319574</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>-14.33</v>
+        <v>-20.03</v>
       </c>
       <c r="L23" t="n">
-        <v>18.76</v>
+        <v>20.03</v>
       </c>
       <c r="M23" t="n">
         <v>3.07</v>
       </c>
       <c r="N23" t="n">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
       <c r="O23" t="n">
         <v>-4.97</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44973</v>
+        <v>44974</v>
       </c>
       <c r="H24" t="n">
-        <v>70.3</v>
+        <v>68.45</v>
       </c>
       <c r="I24" t="n">
         <v>68.59596494855778</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.26</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>11.02</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.45</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H25" t="n">
-        <v>67.05</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>67.34239297591947</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K25" t="n">
-        <v>2.05</v>
+        <v>-0.22</v>
       </c>
       <c r="L25" t="n">
         <v>2.56</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.31</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45068</v>
+        <v>45069</v>
       </c>
       <c r="H26" t="n">
-        <v>115.9</v>
+        <v>113</v>
       </c>
       <c r="I26" t="n">
         <v>113.2634536939266</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>68.95</v>
+        <v>64.72</v>
       </c>
       <c r="L26" t="n">
         <v>1.9</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>20.34</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H27" t="n">
-        <v>128.7</v>
+        <v>136.65</v>
       </c>
       <c r="I27" t="n">
         <v>129.7648354069811</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.89</v>
+        <v>-20.93</v>
       </c>
       <c r="L27" t="n">
-        <v>16.99</v>
+        <v>23.01</v>
       </c>
       <c r="M27" t="n">
         <v>3.5</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>11.56</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H28" t="n">
-        <v>126</v>
+        <v>120.95</v>
       </c>
       <c r="I28" t="n">
         <v>123.1652374433307</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.79</v>
+        <v>-11.49</v>
       </c>
       <c r="L28" t="n">
-        <v>8.529999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="M28" t="n">
         <v>6.15</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.57</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H29" t="n">
-        <v>131.05</v>
+        <v>138.3</v>
       </c>
       <c r="I29" t="n">
         <v>134.284792591132</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.35</v>
+        <v>-14.34</v>
       </c>
       <c r="L29" t="n">
-        <v>9.84</v>
+        <v>14.92</v>
       </c>
       <c r="M29" t="n">
         <v>1.62</v>
       </c>
       <c r="N29" t="n">
-        <v>2.62</v>
+        <v>5.53</v>
       </c>
       <c r="O29" t="n">
         <v>-4.01</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H30" t="n">
-        <v>157.75</v>
+        <v>151.15</v>
       </c>
       <c r="I30" t="n">
         <v>151.2330832956904</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K30" t="n">
-        <v>14.06</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>5.57</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>17.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H31" t="n">
-        <v>165</v>
+        <v>172.4</v>
       </c>
       <c r="I31" t="n">
         <v>171.5145322774417</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.16</v>
+        <v>-14.06</v>
       </c>
       <c r="L31" t="n">
-        <v>13.2</v>
+        <v>16.18</v>
       </c>
       <c r="M31" t="n">
         <v>3.25</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.6</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H32" t="n">
-        <v>259.25</v>
+        <v>229.6</v>
       </c>
       <c r="I32" t="n">
         <v>257.1474218290602</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K32" t="n">
-        <v>50.38</v>
+        <v>33.18</v>
       </c>
       <c r="L32" t="n">
         <v>3.94</v>
@@ -2265,7 +2648,7 @@
         <v>8.41</v>
       </c>
       <c r="N32" t="n">
-        <v>9.859999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="O32" t="n">
         <v>4.48</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>32.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45404</v>
+        <v>45405</v>
       </c>
       <c r="H33" t="n">
-        <v>264.15</v>
+        <v>277.35</v>
       </c>
       <c r="I33" t="n">
         <v>275.8728936517568</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K33" t="n">
-        <v>-15.05</v>
+        <v>-20.8</v>
       </c>
       <c r="L33" t="n">
         <v>22.52</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.85</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H34" t="n">
-        <v>269.95</v>
+        <v>261.05</v>
       </c>
       <c r="I34" t="n">
         <v>261.2321893964269</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.67</v>
+        <v>-5.88</v>
       </c>
       <c r="L34" t="n">
-        <v>5.9</v>
+        <v>6.62</v>
       </c>
       <c r="M34" t="n">
         <v>0.62</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>14.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="H35" t="n">
-        <v>280.25</v>
+        <v>290.8</v>
       </c>
       <c r="I35" t="n">
         <v>289.1436648106457</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.35</v>
+        <v>-11.4</v>
       </c>
       <c r="L35" t="n">
-        <v>8.85</v>
+        <v>12.43</v>
       </c>
       <c r="M35" t="n">
         <v>1.66</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.04</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45512</v>
+        <v>45513</v>
       </c>
       <c r="H36" t="n">
-        <v>538.45</v>
+        <v>518.15</v>
       </c>
       <c r="I36" t="n">
         <v>523.5448376691938</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K36" t="n">
-        <v>85.16</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>3.54</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>20.89</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H37" t="n">
-        <v>411.15</v>
+        <v>426.4</v>
       </c>
       <c r="I37" t="n">
         <v>421.5914863823625</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K37" t="n">
-        <v>20.65</v>
+        <v>17.71</v>
       </c>
       <c r="L37" t="n">
         <v>19.56</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>15.86</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45695</v>
+        <v>45698</v>
       </c>
       <c r="H38" t="n">
-        <v>395.05</v>
+        <v>381.45</v>
       </c>
       <c r="I38" t="n">
         <v>388.316138598007</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.35</v>
+        <v>-10.54</v>
       </c>
       <c r="L38" t="n">
-        <v>9.66</v>
+        <v>11.2</v>
       </c>
       <c r="M38" t="n">
         <v>4.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>20.73</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="H39" t="n">
-        <v>357.05</v>
+        <v>372.8</v>
       </c>
       <c r="I39" t="n">
         <v>364.4903227407816</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K39" t="n">
-        <v>6.4</v>
+        <v>2.27</v>
       </c>
       <c r="L39" t="n">
         <v>4.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.47</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H40" t="n">
-        <v>398</v>
+        <v>381.95</v>
       </c>
       <c r="I40" t="n">
         <v>384.8782957930866</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K40" t="n">
-        <v>6.76</v>
+        <v>2.45</v>
       </c>
       <c r="L40" t="n">
         <v>4.1</v>
@@ -2721,7 +3200,7 @@
         <v>2.85</v>
       </c>
       <c r="N40" t="n">
-        <v>3.81</v>
+        <v>4.03</v>
       </c>
       <c r="O40" t="n">
         <v>4.41</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.7</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H41" t="n">
-        <v>331.85</v>
+        <v>334.6</v>
       </c>
       <c r="I41" t="n">
         <v>334.1031188488013</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>13.12</v>
+        <v>12.4</v>
       </c>
       <c r="L41" t="n">
         <v>6.17</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="H42" t="n">
-        <v>339.15</v>
+        <v>333.05</v>
       </c>
       <c r="I42" t="n">
         <v>334.5491389916041</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>1.36</v>
+        <v>-0.46</v>
       </c>
       <c r="L42" t="n">
         <v>2.85</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H43" t="n">
-        <v>319.15</v>
+        <v>332.5</v>
       </c>
       <c r="I43" t="n">
         <v>324.436965617235</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>4.17</v>
+        <v>0.17</v>
       </c>
       <c r="L43" t="n">
         <v>2.64</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.93</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H44" t="n">
-        <v>342.55</v>
+        <v>332.2</v>
       </c>
       <c r="I44" t="n">
         <v>337.5773714804109</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>3.02</v>
+        <v>-0.09</v>
       </c>
       <c r="L44" t="n">
         <v>4.03</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.55</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H45" t="n">
-        <v>287.06</v>
+        <v>293.89</v>
       </c>
       <c r="I45" t="n">
         <v>290.545923496325</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K45" t="n">
-        <v>13.59</v>
+        <v>11.53</v>
       </c>
       <c r="L45" t="n">
         <v>6.2</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>12.61</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H46" t="n">
-        <v>283</v>
+        <v>276.8</v>
       </c>
       <c r="I46" t="n">
         <v>279.5245686982968</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.71</v>
+        <v>-5.82</v>
       </c>
       <c r="L46" t="n">
-        <v>4.35</v>
+        <v>7.75</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="N46" t="n">
         <v>4.1</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H47" t="n">
-        <v>201.7</v>
+        <v>214.29</v>
       </c>
       <c r="I47" t="n">
         <v>213.6468468935048</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K47" t="n">
-        <v>27.13</v>
+        <v>22.58</v>
       </c>
       <c r="L47" t="n">
         <v>1.32</v>
@@ -3120,7 +3683,7 @@
         <v>3.75</v>
       </c>
       <c r="N47" t="n">
-        <v>4.98</v>
+        <v>6.24</v>
       </c>
       <c r="O47" t="n">
         <v>-2.19</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.76</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H48" t="n">
-        <v>195.87</v>
+        <v>187.2</v>
       </c>
       <c r="I48" t="n">
         <v>195.4889926778544</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.6</v>
+        <v>-12.64</v>
       </c>
       <c r="L48" t="n">
-        <v>9.449999999999999</v>
+        <v>12.78</v>
       </c>
       <c r="M48" t="n">
         <v>0.95</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>4.43</v>
       </c>
       <c r="O48" t="n">
         <v>6.24</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3237,6 +3824,14 @@
       <c r="Q49" t="n">
         <v>14</v>
       </c>
+      <c r="R49" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6461,7 +7056,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.3</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="6">
@@ -6471,7 +7066,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -6481,7 +7076,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
@@ -6491,7 +7086,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -6501,7 +7096,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -6511,7 +7106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119.6</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="11">
@@ -6521,7 +7116,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -6531,7 +7126,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -6541,7 +7136,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="14">
@@ -6551,7 +7146,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.1</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="15">
@@ -6561,7 +7156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.43</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="16">
@@ -6571,7 +7166,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.49</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="17">
@@ -6581,7 +7176,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105.73</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -6591,7 +7186,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.6</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="19">
@@ -6601,7 +7196,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.86</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="20">
@@ -6611,7 +7206,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.9</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="21">
@@ -6621,7 +7216,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.52</v>
+        <v>29.68</v>
       </c>
     </row>
     <row r="22">
@@ -6631,7 +7226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6641,7 +7236,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -6651,7 +7246,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="25">
@@ -6661,7 +7256,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.41</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -6671,7 +7266,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.03</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="27">
@@ -6681,7 +7276,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.11</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="28">
@@ -6691,7 +7286,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
